--- a/data/leagues/AGP 30 2026.xlsx
+++ b/data/leagues/AGP 30 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="113">
   <si>
     <t>Shake N' Bake</t>
   </si>
@@ -55,25 +55,25 @@
     <t>Jimmys</t>
   </si>
   <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +148,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,36 +172,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Jake Guidicy</t>
+  </si>
+  <si>
     <t>Thomas Beck</t>
   </si>
   <si>
     <t>jimmy guinn</t>
   </si>
   <si>
+    <t>Corey Beard</t>
+  </si>
+  <si>
+    <t>Gage Ernst</t>
+  </si>
+  <si>
+    <t>BRANDON AU YONG</t>
+  </si>
+  <si>
     <t>max allen</t>
   </si>
   <si>
-    <t>Jake Guidicy</t>
-  </si>
-  <si>
-    <t>Corey Beard</t>
+    <t>Quentin Stoffel</t>
+  </si>
+  <si>
+    <t>Lance Swearingen</t>
   </si>
   <si>
     <t>Victor pagan</t>
   </si>
   <si>
-    <t>BRANDON AU YONG</t>
-  </si>
-  <si>
-    <t>Gage Ernst</t>
-  </si>
-  <si>
-    <t>Lance Swearingen</t>
-  </si>
-  <si>
-    <t>Quentin Stoffel</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,49 +226,46 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>10.0-4.0</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.9-0.1</t>
   </si>
   <si>
     <t>6.9-7.0-0.1</t>
   </si>
   <si>
-    <t>7.3-6.7-0.1</t>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.3-0.1</t>
   </si>
   <si>
     <t>6.0-7.9-0.1</t>
   </si>
   <si>
-    <t>5.6-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.7-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.1-0.1</t>
+    <t>5.2-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.2-0.1</t>
   </si>
   <si>
     <t>10-4</t>
@@ -274,6 +274,9 @@
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -295,33 +298,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓10</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -777,13 +780,13 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -794,31 +797,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -847,7 +850,7 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
@@ -899,7 +902,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -911,19 +914,19 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -931,34 +934,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -981,19 +984,19 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1004,31 +1007,31 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1039,31 +1042,31 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" t="s">
         <v>11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1074,31 +1077,31 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
       <c r="F11" t="s">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1108,30 +1111,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1165,25 +1168,25 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>26</v>
-      </c>
       <c r="F3">
-        <v>2</v>
+        <v>-19</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1191,25 +1194,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1217,25 +1220,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>19</v>
       </c>
       <c r="F5">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1243,25 +1246,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1269,25 +1272,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
         <v>-2</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
       <c r="G7">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1295,25 +1298,25 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
       <c r="F8">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1321,25 +1324,77 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>-2</v>
+      </c>
+      <c r="F9">
+        <v>-12</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="F9">
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>-2</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>8</v>
+      <c r="F11">
+        <v>-5</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1368,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1382,13 +1437,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1396,13 +1451,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1410,13 +1465,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1424,13 +1479,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1441,7 +1496,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1455,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1469,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1480,13 +1535,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1494,13 +1549,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1535,10 +1590,10 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="D2">
-        <v>0.5999999999999996</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1549,13 +1604,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="D3">
-        <v>0.7999999999999998</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -1569,13 +1624,13 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1583,16 +1638,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D5">
-        <v>0.2000000000000002</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1603,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>-0.7999999999999998</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1617,16 +1672,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D7">
-        <v>-0.1000000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1634,16 +1689,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D8">
-        <v>-0.2999999999999998</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1651,13 +1706,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D9">
-        <v>0.3999999999999999</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1668,13 +1723,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="D10">
-        <v>0.1000000000000001</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1688,10 +1743,10 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D11">
-        <v>0.6000000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1750,25 +1805,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>52</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C2">
-        <v>24.3</v>
+        <v>17.2</v>
       </c>
       <c r="D2">
-        <v>12.7</v>
+        <v>5.4</v>
       </c>
       <c r="E2">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="F2">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1780,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1788,303 +1843,303 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>26.7</v>
+        <v>14.3</v>
       </c>
       <c r="C3">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="F3">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
+        <v>0.7</v>
+      </c>
+      <c r="J3">
         <v>0.4</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
-        <v>98.59999999999999</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>14.8</v>
+        <v>6.3</v>
       </c>
       <c r="C4">
-        <v>26.6</v>
+        <v>18.4</v>
       </c>
       <c r="D4">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="E4">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="F4">
-        <v>8.6</v>
+        <v>15.6</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="K4">
         <v>0.2</v>
       </c>
       <c r="L4">
-        <v>95.09999999999999</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="C5">
-        <v>7.5</v>
+        <v>14.2</v>
       </c>
       <c r="D5">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="E5">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="F5">
-        <v>18.8</v>
+        <v>14.9</v>
       </c>
       <c r="G5">
-        <v>14.8</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="L5">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="C6">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E6">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>16.3</v>
       </c>
       <c r="G6">
-        <v>17.4</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="I6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="L6">
-        <v>71.7</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="C7">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>10.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E7">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="F7">
-        <v>17.8</v>
+        <v>15.1</v>
       </c>
       <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
         <v>17.3</v>
       </c>
-      <c r="H7">
-        <v>15.3</v>
-      </c>
       <c r="I7">
-        <v>10.6</v>
+        <v>12.7</v>
       </c>
       <c r="J7">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K7">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>66.90000000000001</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="D8">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="E8">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F8">
-        <v>8.699999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>14.3</v>
       </c>
       <c r="H8">
-        <v>21.3</v>
+        <v>16.6</v>
       </c>
       <c r="I8">
-        <v>20.6</v>
+        <v>16.5</v>
       </c>
       <c r="J8">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>33.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D9">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="E9">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="F9">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="G9">
-        <v>14.5</v>
+        <v>16.3</v>
       </c>
       <c r="H9">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="I9">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="J9">
-        <v>18.3</v>
+        <v>16.2</v>
       </c>
       <c r="K9">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>0.1</v>
       </c>
-      <c r="C10">
-        <v>0.3</v>
-      </c>
       <c r="D10">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E10">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
+        <v>5.9</v>
+      </c>
+      <c r="H10">
         <v>9.4</v>
       </c>
-      <c r="H10">
-        <v>15.5</v>
-      </c>
       <c r="I10">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>28.5</v>
+        <v>26.7</v>
       </c>
       <c r="K10">
-        <v>17.9</v>
+        <v>34</v>
       </c>
       <c r="L10">
-        <v>19.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2098,31 +2153,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="I11">
-        <v>9.4</v>
+        <v>15.2</v>
       </c>
       <c r="J11">
-        <v>21.9</v>
+        <v>23.8</v>
       </c>
       <c r="K11">
-        <v>61.4</v>
+        <v>42.4</v>
       </c>
       <c r="L11">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
     </row>
   </sheetData>
@@ -2132,10 +2187,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2157,8 +2212,11 @@
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2172,7 +2230,7 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F2">
         <v>99.90000000000001</v>
@@ -2181,241 +2239,271 @@
         <v>99.3</v>
       </c>
       <c r="H2">
-        <v>99.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.8</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="C3">
-        <v>27.8</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>86.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="E3">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="F3">
-        <v>97.7</v>
+        <v>98.3</v>
       </c>
       <c r="G3">
-        <v>98.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H3">
+        <v>96.2</v>
+      </c>
+      <c r="I3">
+        <v>95.89999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>8.6</v>
+      </c>
+      <c r="C4">
+        <v>89.3</v>
+      </c>
+      <c r="D4">
+        <v>66.7</v>
+      </c>
+      <c r="E4">
+        <v>37.1</v>
+      </c>
+      <c r="F4">
+        <v>54.2</v>
+      </c>
+      <c r="G4">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H4">
+        <v>90</v>
+      </c>
+      <c r="I4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>33.2</v>
+      </c>
+      <c r="C5">
+        <v>98.5</v>
+      </c>
+      <c r="D5">
+        <v>99.7</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="G5">
+        <v>97</v>
+      </c>
+      <c r="H5">
+        <v>82.19999999999999</v>
+      </c>
+      <c r="I5">
+        <v>78.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>83.5</v>
+      </c>
+      <c r="C6">
+        <v>10.9</v>
+      </c>
+      <c r="D6">
+        <v>17.2</v>
+      </c>
+      <c r="E6">
+        <v>74.8</v>
+      </c>
+      <c r="F6">
+        <v>55.7</v>
+      </c>
+      <c r="G6">
+        <v>74.2</v>
+      </c>
+      <c r="H6">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I6">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C7">
+        <v>68.2</v>
+      </c>
+      <c r="D7">
+        <v>51.6</v>
+      </c>
+      <c r="E7">
+        <v>91</v>
+      </c>
+      <c r="F7">
+        <v>59.3</v>
+      </c>
+      <c r="G7">
+        <v>26.8</v>
+      </c>
+      <c r="H7">
+        <v>55.1</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>98.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>33.3</v>
-      </c>
-      <c r="C4">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="D4">
-        <v>99.7</v>
-      </c>
-      <c r="E4">
+      <c r="C8">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D8">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="E8">
+        <v>53.3</v>
+      </c>
+      <c r="F8">
+        <v>89.2</v>
+      </c>
+      <c r="G8">
+        <v>70</v>
+      </c>
+      <c r="H8">
+        <v>41.8</v>
+      </c>
+      <c r="I8">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
         <v>100</v>
       </c>
-      <c r="F4">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="G4">
-        <v>97.2</v>
-      </c>
-      <c r="H4">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>85</v>
-      </c>
-      <c r="C5">
-        <v>10.2</v>
-      </c>
-      <c r="D5">
-        <v>20.4</v>
-      </c>
-      <c r="E5">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="F5">
-        <v>52.90000000000001</v>
-      </c>
-      <c r="G5">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="H5">
-        <v>78.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>7.8</v>
-      </c>
-      <c r="C6">
-        <v>88.3</v>
-      </c>
-      <c r="D6">
-        <v>64.8</v>
-      </c>
-      <c r="E6">
-        <v>36.9</v>
-      </c>
-      <c r="F6">
-        <v>52.2</v>
-      </c>
-      <c r="G6">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="H6">
-        <v>72.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>97.7</v>
-      </c>
-      <c r="C7">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D7">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E7">
-        <v>53.6</v>
-      </c>
-      <c r="F7">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="G7">
-        <v>70.8</v>
-      </c>
-      <c r="H7">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
+      <c r="C9">
+        <v>62.4</v>
+      </c>
+      <c r="D9">
+        <v>27.3</v>
+      </c>
+      <c r="E9">
+        <v>2.9</v>
+      </c>
+      <c r="F9">
+        <v>2.7</v>
+      </c>
+      <c r="G9">
+        <v>16.9</v>
+      </c>
+      <c r="H9">
+        <v>40.5</v>
+      </c>
+      <c r="I9">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8">
-        <v>46</v>
-      </c>
-      <c r="D8">
-        <v>60</v>
-      </c>
-      <c r="E8">
-        <v>34.59999999999999</v>
-      </c>
-      <c r="F8">
-        <v>34.59999999999999</v>
-      </c>
-      <c r="G8">
-        <v>37</v>
-      </c>
-      <c r="H8">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="C9">
-        <v>66.7</v>
-      </c>
-      <c r="D9">
-        <v>48.8</v>
-      </c>
-      <c r="E9">
-        <v>90.5</v>
-      </c>
-      <c r="F9">
-        <v>61.8</v>
-      </c>
-      <c r="G9">
-        <v>27.3</v>
-      </c>
-      <c r="H9">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10">
-        <v>66.5</v>
+        <v>48.4</v>
       </c>
       <c r="D10">
-        <v>28.1</v>
+        <v>60.9</v>
       </c>
       <c r="E10">
-        <v>3.3</v>
+        <v>33.6</v>
       </c>
       <c r="F10">
-        <v>3.5</v>
+        <v>32.6</v>
       </c>
       <c r="G10">
-        <v>14.9</v>
+        <v>36.7</v>
       </c>
       <c r="H10">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>11.9</v>
+      </c>
+      <c r="I10">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D11">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="E11">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="F11">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
-        <v>2.6</v>
+        <v>11.4</v>
+      </c>
+      <c r="I11">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2433,25 +2521,25 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2459,28 +2547,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>135.18</v>
+        <v>126.93</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>140.36</v>
+        <v>144.01</v>
       </c>
       <c r="G2">
-        <v>0.479</v>
+        <v>0.51</v>
       </c>
       <c r="H2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2488,28 +2576,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>145.6</v>
+        <v>139.94</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>140.36</v>
+        <v>139.2</v>
       </c>
       <c r="G3">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2517,28 +2605,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>133.4</v>
+        <v>142.41</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>142.29</v>
+        <v>138.87</v>
       </c>
       <c r="G4">
-        <v>0.479</v>
+        <v>0.469</v>
       </c>
       <c r="H4">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2546,28 +2634,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>131.92</v>
+        <v>145.2</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5">
-        <v>142.29</v>
+        <v>140.25</v>
       </c>
       <c r="G5">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H5">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2575,28 +2663,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>142.1</v>
+        <v>148.77</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>141.8</v>
+        <v>140.82</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2604,28 +2692,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>127.1</v>
+        <v>134.83</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>141.8</v>
+        <v>141.31</v>
       </c>
       <c r="G7">
-        <v>0.542</v>
+        <v>0.531</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2633,28 +2721,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>130.71</v>
+        <v>129.86</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>139.63</v>
+        <v>140.63</v>
       </c>
       <c r="G8">
-        <v>0.521</v>
+        <v>0.469</v>
       </c>
       <c r="H8">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2662,28 +2750,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>155.85</v>
+        <v>142.93</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>139.63</v>
+        <v>136.9</v>
       </c>
       <c r="G9">
-        <v>0.521</v>
+        <v>0.49</v>
       </c>
       <c r="H9">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2694,25 +2782,25 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>159.39</v>
+        <v>158.48</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10">
-        <v>137.73</v>
+        <v>138.34</v>
       </c>
       <c r="G10">
-        <v>0.479</v>
+        <v>0.469</v>
       </c>
       <c r="H10">
-        <v>-3.6</v>
+        <v>-2.6</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2720,28 +2808,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11">
+        <v>130.31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>139.34</v>
+      </c>
+      <c r="G11">
+        <v>0.531</v>
+      </c>
+      <c r="H11">
+        <v>-2.9</v>
+      </c>
+      <c r="I11">
         <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11">
-        <v>142.38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11">
-        <v>137.73</v>
-      </c>
-      <c r="G11">
-        <v>0.479</v>
-      </c>
-      <c r="H11">
-        <v>-3.6</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2759,28 +2847,28 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2788,19 +2876,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>159.3933333333333</v>
+        <v>158.48</v>
       </c>
       <c r="E2">
-        <v>956.3600000000001</v>
+        <v>1109.36</v>
       </c>
       <c r="F2">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2820,45 +2908,45 @@
         <v>67</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>145.6</v>
+        <v>142.4142857142857</v>
       </c>
       <c r="E3">
-        <v>873.6</v>
+        <v>996.9</v>
       </c>
       <c r="F3">
-        <v>98.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
         <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>155.85</v>
+        <v>145.2</v>
       </c>
       <c r="E4">
-        <v>935.0999999999999</v>
+        <v>1016.4</v>
       </c>
       <c r="F4">
-        <v>95.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="G4">
         <v>0.2</v>
@@ -2867,181 +2955,181 @@
         <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D5">
-        <v>142.3833333333334</v>
+        <v>148.7714285714285</v>
       </c>
       <c r="E5">
-        <v>854.3000000000001</v>
+        <v>1041.4</v>
       </c>
       <c r="F5">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="G5">
-        <v>1.3</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H5" t="s">
         <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>142.1</v>
+        <v>142.9285714285714</v>
       </c>
       <c r="E6">
-        <v>852.5999999999999</v>
+        <v>1000.5</v>
       </c>
       <c r="F6">
-        <v>71.7</v>
+        <v>71.2</v>
       </c>
       <c r="G6">
-        <v>0.8999999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="s">
         <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>133.4</v>
+        <v>139.9428571428571</v>
       </c>
       <c r="E7">
-        <v>800.4000000000001</v>
+        <v>979.5999999999999</v>
       </c>
       <c r="F7">
-        <v>66.90000000000001</v>
+        <v>56.39999999999999</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="H7" t="s">
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>131.9166666666667</v>
+        <v>129.8571428571429</v>
       </c>
       <c r="E8">
-        <v>791.5</v>
+        <v>909.0000000000001</v>
       </c>
       <c r="F8">
-        <v>33.5</v>
+        <v>47.9</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="s">
         <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D9">
-        <v>135.1833333333333</v>
+        <v>134.8257142857143</v>
       </c>
       <c r="E9">
-        <v>811.0999999999999</v>
+        <v>943.78</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>37.8</v>
       </c>
       <c r="G9">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="H9" t="s">
         <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D10">
-        <v>130.7133333333333</v>
+        <v>126.9285714285714</v>
       </c>
       <c r="E10">
-        <v>784.28</v>
+        <v>888.5</v>
       </c>
       <c r="F10">
-        <v>19.8</v>
+        <v>11.9</v>
       </c>
       <c r="G10">
-        <v>17.9</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
         <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3052,25 +3140,25 @@
         <v>70</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D11">
-        <v>127.1</v>
+        <v>130.3142857142857</v>
       </c>
       <c r="E11">
-        <v>762.6</v>
+        <v>912.2</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
       <c r="G11">
-        <v>61.4</v>
+        <v>42.4</v>
       </c>
       <c r="H11" t="s">
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3088,16 +3176,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3108,7 +3196,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>26</v>
@@ -3117,7 +3205,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3128,16 +3216,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3151,13 +3239,13 @@
         <v>52</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3168,16 +3256,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3188,16 +3276,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3208,10 +3296,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -3228,13 +3316,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>95</v>
@@ -3251,7 +3339,7 @@
         <v>54</v>
       </c>
       <c r="D9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3268,13 +3356,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>97</v>
@@ -3288,10 +3376,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3307,10 +3395,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -3330,10 +3418,13 @@
         <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3355,11 +3446,14 @@
       <c r="G2">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -3381,11 +3475,14 @@
       <c r="G3">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3407,11 +3504,14 @@
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -3433,11 +3533,14 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3459,11 +3562,14 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>-2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3485,11 +3591,14 @@
       <c r="G7">
         <v>-2</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7">
+        <v>-5</v>
+      </c>
+      <c r="I7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3511,11 +3620,14 @@
       <c r="G8">
         <v>-6</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8">
+        <v>-5</v>
+      </c>
+      <c r="I8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -3537,11 +3649,14 @@
       <c r="G9">
         <v>-11</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9">
+        <v>-12</v>
+      </c>
+      <c r="I9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -3563,11 +3678,14 @@
       <c r="G10">
         <v>-12</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>-14</v>
+      </c>
+      <c r="I10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -3589,7 +3707,10 @@
       <c r="G11">
         <v>-25</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11">
+        <v>-19</v>
+      </c>
+      <c r="I11" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/leagues/AGP 30 2026.xlsx
+++ b/data/leagues/AGP 30 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="112">
   <si>
     <t>Shake N' Bake</t>
   </si>
@@ -238,10 +238,10 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>10.0-4.0</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
+    <t>10.0-4.0-0.1</t>
+  </si>
+  <si>
+    <t>8.8-5.2-0.1</t>
   </si>
   <si>
     <t>7.8-6.1-0.1</t>
@@ -256,13 +256,13 @@
     <t>6.5-7.4-0.1</t>
   </si>
   <si>
-    <t>6.7-7.3-0.1</t>
+    <t>6.6-7.3-0.1</t>
   </si>
   <si>
     <t>6.0-7.9-0.1</t>
   </si>
   <si>
-    <t>5.2-8.8-0.1</t>
+    <t>5.3-8.7-0.1</t>
   </si>
   <si>
     <t>4.8-9.2-0.1</t>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>5-9</t>
-  </si>
-  <si>
-    <t>4-10</t>
   </si>
   <si>
     <t>Owners</t>
@@ -1116,25 +1113,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1805,25 +1802,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>73.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C2">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="D2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="E2">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1835,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1843,37 +1840,37 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>14.3</v>
+        <v>17.1</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30.1</v>
       </c>
       <c r="D3">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="E3">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>95.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1881,37 +1878,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="C4">
-        <v>18.4</v>
+        <v>19.3</v>
       </c>
       <c r="D4">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="F4">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L4">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1919,37 +1916,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="D5">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5">
-        <v>19.3</v>
+        <v>16.4</v>
       </c>
       <c r="F5">
-        <v>14.9</v>
+        <v>17.8</v>
       </c>
       <c r="G5">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L5">
-        <v>79</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1957,37 +1954,37 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D6">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="E6">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="F6">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="H6">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="I6">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K6">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="L6">
-        <v>71.2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1995,37 +1992,37 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D7">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="E7">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="F7">
-        <v>15.1</v>
+        <v>16.3</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="H7">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="I7">
-        <v>12.7</v>
+        <v>9.9</v>
       </c>
       <c r="J7">
         <v>9.199999999999999</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
-        <v>56.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2033,37 +2030,37 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
         <v>7.5</v>
       </c>
       <c r="E8">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F8">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="G8">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="H8">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
       <c r="I8">
-        <v>16.5</v>
+        <v>19.2</v>
       </c>
       <c r="J8">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L8">
-        <v>47.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2071,37 +2068,37 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C9">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E9">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="F9">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9">
-        <v>16.3</v>
+        <v>13.1</v>
       </c>
       <c r="H9">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
       <c r="I9">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="J9">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="K9">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="L9">
-        <v>37.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2112,34 +2109,34 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G10">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="H10">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>16.4</v>
       </c>
       <c r="J10">
-        <v>26.7</v>
+        <v>29.2</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>30.3</v>
       </c>
       <c r="L10">
-        <v>11.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2153,31 +2150,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="H11">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I11">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="J11">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="K11">
-        <v>42.4</v>
+        <v>44.2</v>
       </c>
       <c r="L11">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>
@@ -2221,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2233,13 +2230,13 @@
         <v>99.90000000000001</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -2250,28 +2247,28 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>69.5</v>
+        <v>71.39999999999999</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>27.4</v>
       </c>
       <c r="D3">
-        <v>85.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E3">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="F3">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="G3">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H3">
         <v>95.7</v>
       </c>
-      <c r="F3">
-        <v>98.3</v>
-      </c>
-      <c r="G3">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="H3">
-        <v>96.2</v>
-      </c>
       <c r="I3">
-        <v>95.89999999999999</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2279,28 +2276,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="C4">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D4">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="E4">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="F4">
-        <v>54.2</v>
+        <v>51.4</v>
       </c>
       <c r="G4">
-        <v>77.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I4">
-        <v>89</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2308,28 +2305,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>33.2</v>
+        <v>30.7</v>
       </c>
       <c r="C5">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="D5">
-        <v>99.7</v>
+        <v>99.2</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F5">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G5">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="H5">
-        <v>82.19999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I5">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2337,28 +2334,28 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>83.5</v>
+        <v>85</v>
       </c>
       <c r="C6">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="D6">
-        <v>17.2</v>
+        <v>20.8</v>
       </c>
       <c r="E6">
-        <v>74.8</v>
+        <v>70.5</v>
       </c>
       <c r="F6">
-        <v>55.7</v>
+        <v>51.4</v>
       </c>
       <c r="G6">
-        <v>74.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H6">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I6">
-        <v>71.8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2366,28 +2363,28 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>7.000000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C7">
-        <v>68.2</v>
+        <v>69.5</v>
       </c>
       <c r="D7">
-        <v>51.6</v>
+        <v>49.3</v>
       </c>
       <c r="E7">
         <v>91</v>
       </c>
       <c r="F7">
-        <v>59.3</v>
+        <v>59.9</v>
       </c>
       <c r="G7">
-        <v>26.8</v>
+        <v>27.9</v>
       </c>
       <c r="H7">
-        <v>55.1</v>
+        <v>58.7</v>
       </c>
       <c r="I7">
-        <v>60</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2395,28 +2392,28 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>98.2</v>
+        <v>97.2</v>
       </c>
       <c r="C8">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D8">
-        <v>89.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E8">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="F8">
-        <v>89.2</v>
+        <v>90.3</v>
       </c>
       <c r="G8">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H8">
-        <v>41.8</v>
+        <v>43.2</v>
       </c>
       <c r="I8">
-        <v>48.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2427,25 +2424,25 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>62.4</v>
+        <v>60.9</v>
       </c>
       <c r="D9">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="E9">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="F9">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="H9">
-        <v>40.5</v>
+        <v>38.3</v>
       </c>
       <c r="I9">
-        <v>34.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2456,25 +2453,25 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>48.4</v>
+        <v>49.4</v>
       </c>
       <c r="D10">
-        <v>60.9</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="E10">
-        <v>33.6</v>
+        <v>36.4</v>
       </c>
       <c r="F10">
-        <v>32.6</v>
+        <v>35.4</v>
       </c>
       <c r="G10">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="H10">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="I10">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2482,28 +2479,28 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>21.2</v>
+        <v>18.8</v>
       </c>
       <c r="D11">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="E11">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F11">
-        <v>8.5</v>
+        <v>10.3</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="H11">
-        <v>11.4</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="I11">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2885,7 @@
         <v>1109.36</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2917,10 +2914,10 @@
         <v>996.9</v>
       </c>
       <c r="F3">
-        <v>95.8</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>72</v>
@@ -2946,10 +2943,10 @@
         <v>1016.4</v>
       </c>
       <c r="F4">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="s">
         <v>73</v>
@@ -2975,10 +2972,10 @@
         <v>1041.4</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="G5">
-        <v>0.7000000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H5" t="s">
         <v>74</v>
@@ -3004,10 +3001,10 @@
         <v>1000.5</v>
       </c>
       <c r="F6">
-        <v>71.2</v>
+        <v>71</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="s">
         <v>75</v>
@@ -3033,16 +3030,16 @@
         <v>979.5999999999999</v>
       </c>
       <c r="F7">
-        <v>56.39999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="G7">
-        <v>4.399999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="s">
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3062,10 +3059,10 @@
         <v>909.0000000000001</v>
       </c>
       <c r="F8">
-        <v>47.9</v>
+        <v>46</v>
       </c>
       <c r="G8">
-        <v>6.4</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="H8" t="s">
         <v>77</v>
@@ -3091,10 +3088,10 @@
         <v>943.78</v>
       </c>
       <c r="F9">
-        <v>37.8</v>
+        <v>36.2</v>
       </c>
       <c r="G9">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="H9" t="s">
         <v>78</v>
@@ -3120,10 +3117,10 @@
         <v>888.5</v>
       </c>
       <c r="F10">
-        <v>11.9</v>
+        <v>13.8</v>
       </c>
       <c r="G10">
-        <v>34</v>
+        <v>30.3</v>
       </c>
       <c r="H10" t="s">
         <v>79</v>
@@ -3149,16 +3146,16 @@
         <v>912.2</v>
       </c>
       <c r="F11">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="G11">
-        <v>42.4</v>
+        <v>44.2</v>
       </c>
       <c r="H11" t="s">
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3176,16 +3173,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3205,7 +3202,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3225,7 +3222,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3245,7 +3242,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3265,7 +3262,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3285,7 +3282,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3305,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3325,7 +3322,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3345,7 +3342,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3365,7 +3362,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3385,7 +3382,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3400,28 +3397,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3450,7 +3447,7 @@
         <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3479,7 +3476,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3508,7 +3505,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3537,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3566,7 +3563,7 @@
         <v>-2</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3595,7 +3592,7 @@
         <v>-5</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3624,7 +3621,7 @@
         <v>-5</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3653,7 +3650,7 @@
         <v>-12</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3682,7 +3679,7 @@
         <v>-14</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3711,7 +3708,7 @@
         <v>-19</v>
       </c>
       <c r="I11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
